--- a/V5.0_双人执行工作区/00_共享/每日协调/DAILY_GATE_STATUS_20260831.xlsx
+++ b/V5.0_双人执行工作区/00_共享/每日协调/DAILY_GATE_STATUS_20260831.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门槛状态" sheetId="1" r:id="Rd8ddd48edefa4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门槛状态" sheetId="1" r:id="R3738a17a5ec343c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -47,8 +47,20 @@
       <x:color rgb="FFD0021B"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF177A3F"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFC62828"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -83,6 +95,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFDEBEC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9F7E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDE3E3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -92,7 +114,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -134,6 +156,18 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -510,17 +544,17 @@
       <x:c r="D2" s="1" t="str">
         <x:v>A00证据包 + B独立复核</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="11" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
         <x:v>已升级</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
-        <x:v>✅ 2026-08-22</x:v>
+        <x:v>✅ B 2026-08-22</x:v>
       </x:c>
       <x:c r="H2" s="1" t="str">
-        <x:v>✅ 2026-08-23</x:v>
+        <x:v>✅ A 2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
@@ -536,17 +570,17 @@
       <x:c r="D3" s="1" t="str">
         <x:v>A01/A02证据包 + B_REVIEW_A01_A02_20260824</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
-        <x:v>PASS（延期；回签待补）</x:v>
+      <x:c r="E3" s="11" t="str">
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
-        <x:v>保持PASS，补交叉回签</x:v>
+        <x:v>交叉回签已闭环</x:v>
       </x:c>
       <x:c r="G3" s="1" t="str">
-        <x:v>✅ 2026-08-24</x:v>
+        <x:v>✅ B 2026-08-24</x:v>
       </x:c>
       <x:c r="H3" s="1" t="str">
-        <x:v>待交叉回签</x:v>
+        <x:v>✅ A 2026-09-01 交叉回签</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="76" customHeight="1">
@@ -562,11 +596,11 @@
       <x:c r="D4" s="1" t="str">
         <x:v>G2_START_RELEASE_20260828.md + B00_RECEIPT_CHECK_20260827 + A_PROGRESS_SIGNOFF_20260829</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="E4" s="11" t="str">
         <x:v>PASS（启动放行）</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
-        <x:v>允许B建设DB03/DB05/DB06及AI配置；旧缺口继续跟踪，未复核指标不锁数</x:v>
+        <x:v>允许后续页面和AI建设；未复核指标不锁数</x:v>
       </x:c>
       <x:c r="G4" s="1" t="str">
         <x:v>✅ B 2026-08-28</x:v>
@@ -577,7 +611,7 @@
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" s="1" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="B5" s="1" t="str">
         <x:v>G3 六页初验</x:v>
@@ -586,24 +620,24 @@
         <x:v>六页可开；每页≤4组件；筛选/来源/边界可用</x:v>
       </x:c>
       <x:c r="D5" s="1" t="str">
-        <x:v>A_数据平台/当前进度.md + B_REVIEW_A05_A07_20260831 + DB03_ACCEPTANCE_V50 + DB05预验收 + B_DB06_PREACCEPTANCE_20260830</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>BLOCKED（六页主体已完成；正式初验未闭环）</x:v>
+        <x:v>DB01/02 B复核 + DB03/05双签 + DB06关系复核 + B_DB04_FORMAL_REVIEW_20260901</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>不重复搭页；B补DB03/DB05证据并复核A三页，A核查DB06关系；A/B本人签收后再升级</x:v>
+        <x:v>六页初验闭环；进入G4/G5</x:v>
       </x:c>
       <x:c r="G5" s="1" t="str">
-        <x:v>待B本人确认</x:v>
+        <x:v>✅ B 2026-09-02</x:v>
       </x:c>
       <x:c r="H5" s="1" t="str">
-        <x:v>待A过目/复核</x:v>
+        <x:v>✅ A 2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="1" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="B6" s="1" t="str">
         <x:v>G4 AIChat初验</x:v>
@@ -612,24 +646,24 @@
         <x:v>25问全测；数值≥90%；关键误差≤1%；拒答全对</x:v>
       </x:c>
       <x:c r="D6" s="1" t="str">
-        <x:v>B_B04_MATERIAL_READY_20260830 + 25/25离线基准；正式AIP/KB/AGENT未配置，正式实测0/25</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>BLOCKED（0/25）</x:v>
+        <x:v>A侧R19：AI-01/04/16/17 PASS；AI-19/20受20步上限阻塞；B正式全量未完成</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="str">
+        <x:v>BLOCKED（A短链4题通过；长题/全量未闭环）</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>B先创建、发布并冻结AIP/KB/AGENT，完成5题冒烟后再逐题实测；离线基准不算实测</x:v>
+        <x:v>B独立复测六题并跑25/25；不得以A自测代签</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
-        <x:v>待B执行</x:v>
+        <x:v>B_RETEST_REQUIRED</x:v>
       </x:c>
       <x:c r="H6" s="1" t="str">
-        <x:v>待A复核</x:v>
+        <x:v>A已提交修复；不签G4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="1" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="B7" s="1" t="str">
         <x:v>G5 恢复与材料</x:v>
@@ -638,16 +672,16 @@
         <x:v>干净恢复；KPI一致；报告视频合规齐全</x:v>
       </x:c>
       <x:c r="D7" s="1" t="str">
-        <x:v>A07六页页面XML分包已归档；AI资源分包、干净目标独立恢复和报告视频收口未完成</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
+        <x:v>六页XML两分包已核验；AI资源分包、干净目标独立恢复、报告视频未闭环</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>先闭环AI资源和干净恢复，再收口报告、视频与合规材料</x:v>
+        <x:v>闭环AI资源和干净恢复，再收口报告、视频与合规材料</x:v>
       </x:c>
       <x:c r="G7" s="1" t="str">
-        <x:v>待B执行</x:v>
+        <x:v>待B执行/复核</x:v>
       </x:c>
       <x:c r="H7" s="1" t="str">
         <x:v>待A执行/复核</x:v>
@@ -655,7 +689,7 @@
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="1" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="B8" s="1" t="str">
         <x:v>G6 最终放行</x:v>
@@ -664,13 +698,13 @@
         <x:v>双人交叉复核；硬失败0；清单哈希截图齐全</x:v>
       </x:c>
       <x:c r="D8" s="1" t="str">
-        <x:v>G3-G5均未通过；最终清单、哈希和双签未形成</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
+        <x:v>G3已通过；G4、G5未通过；最终清单、哈希和双签未形成</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
-        <x:v>不得标完成；只按真实缺口推进</x:v>
+        <x:v>不得标完成；先闭环G4/G5</x:v>
       </x:c>
       <x:c r="G8" s="1" t="str">
         <x:v>待B签收</x:v>

--- a/V5.0_双人执行工作区/00_共享/每日协调/DAILY_GATE_STATUS_20260831.xlsx
+++ b/V5.0_双人执行工作区/00_共享/每日协调/DAILY_GATE_STATUS_20260831.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门槛状态" sheetId="1" r:id="R3738a17a5ec343c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门槛状态" sheetId="1" r:id="R475578af237a4740"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -646,19 +646,19 @@
         <x:v>25问全测；数值≥90%；关键误差≤1%；拒答全对</x:v>
       </x:c>
       <x:c r="D6" s="1" t="str">
-        <x:v>A侧R19：AI-01/04/16/17 PASS；AI-19/20受20步上限阻塞；B正式全量未完成</x:v>
+        <x:v>A侧R20真实问数：AI-01/04/17 PASS；AI-16/19/20 FAIL；B全量未开始</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
-        <x:v>BLOCKED（A短链4题通过；长题/全量未闭环）</x:v>
+        <x:v>BLOCKED（R20 3题通过、3题失败）</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>B独立复测六题并跑25/25；不得以A自测代签</x:v>
+        <x:v>A先修复AI-16/19/20并重跑全过；再交B独立复测和25/25</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
-        <x:v>B_RETEST_REQUIRED</x:v>
+        <x:v>B_RETEST_NOT_READY</x:v>
       </x:c>
       <x:c r="H6" s="1" t="str">
-        <x:v>A已提交修复；不签G4</x:v>
+        <x:v>A已完成R20复测；3 FAIL，不签G4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
